--- a/data/create-cases.xlsx
+++ b/data/create-cases.xlsx
@@ -1,43 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgosai\dhavalautomation-main\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACEB0EE-270B-4ED8-8DB8-6B271B65366A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-15510" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Account Name</t>
+  </si>
+  <si>
+    <t>Asset</t>
+  </si>
+  <si>
+    <t>Sub Asset</t>
+  </si>
+  <si>
+    <t>Case Type</t>
+  </si>
+  <si>
+    <t>Sub Type</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Dhaval Gosai</t>
+  </si>
+  <si>
+    <t>Ain Dubai</t>
+  </si>
+  <si>
+    <t>AD - Marketing</t>
+  </si>
+  <si>
+    <t>Influencer Visit</t>
+  </si>
+  <si>
+    <t>Vincent Aslarona</t>
+  </si>
+  <si>
+    <t>AinDubai-D2204-NR-AssignedToAsset</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,14 +108,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,64 +449,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.9140625" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.9140625" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>User</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Subject</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Account Name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Asset</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Sub Asset</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Case Type</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Sub Type</v>
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v>Testing 220626 01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Testing</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Dhaval Gosai</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Ain Dubai</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>AD - Marketing</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Influencer Visit</v>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError sqref="A1:H1 D2:H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/create-cases.xlsx
+++ b/data/create-cases.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgosai\dhavalautomation-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACEB0EE-270B-4ED8-8DB8-6B271B65366A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDCF9B9-F4EC-4BE0-A3FD-DB0D6BF6F3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15510" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15030" yWindow="-14790" windowWidth="22650" windowHeight="12855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>User</t>
   </si>
@@ -65,6 +78,63 @@
   </si>
   <si>
     <t>AinDubai-D2204-NR-AssignedToAsset</t>
+  </si>
+  <si>
+    <t>Test Call Center Team Lead Manager</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-NR-AssignedToAsset</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-NR-OnHold</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-NR-InProgress</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-NR-Closed</t>
+  </si>
+  <si>
+    <t>Test Guest Experience Team Lead/Supervisor</t>
+  </si>
+  <si>
+    <t>Ivaylo Saraliev</t>
+  </si>
+  <si>
+    <t>AD - Incident</t>
+  </si>
+  <si>
+    <t>Medical (Low)</t>
+  </si>
+  <si>
+    <t>AD - Complaints</t>
+  </si>
+  <si>
+    <t>Serious, Escalated or VIP</t>
+  </si>
+  <si>
+    <t>Collaboration</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-Ref-Reopened</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-Ref-Escalated</t>
+  </si>
+  <si>
+    <t>AinDubai-D2206-Ref-Cancelled</t>
+  </si>
+  <si>
+    <t>AD - Ticketing</t>
+  </si>
+  <si>
+    <t>Change of date</t>
+  </si>
+  <si>
+    <t>Double payment</t>
+  </si>
+  <si>
+    <t>Attraction closure</t>
   </si>
 </sst>
 </file>
@@ -108,9 +178,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,12 +521,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" customWidth="1"/>
+    <col min="2" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
@@ -463,7 +533,7 @@
     <col min="8" max="8" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,30 +559,180 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f>B3</f>
+        <v>AinDubai-D2206-NR-OnHold</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f t="shared" ref="C4:C8" si="0">B4</f>
+        <v>AinDubai-D2206-NR-InProgress</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>AinDubai-D2206-NR-Closed</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>AinDubai-D2206-Ref-Reopened</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>AinDubai-D2206-Ref-Escalated</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>AinDubai-D2206-Ref-Cancelled</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/create-cases.xlsx
+++ b/data/create-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgosai\dhavalautomation-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDCF9B9-F4EC-4BE0-A3FD-DB0D6BF6F3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFD6E08-844B-409D-B706-54E04F6966F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15030" yWindow="-14790" windowWidth="22650" windowHeight="12855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15510" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>User</t>
   </si>
@@ -53,105 +53,97 @@
     <t>Sub Asset</t>
   </si>
   <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Sub-Area</t>
+  </si>
+  <si>
     <t>Case Type</t>
   </si>
   <si>
     <t>Sub Type</t>
   </si>
   <si>
-    <t/>
+    <t>Case Number</t>
+  </si>
+  <si>
+    <t>Test Call Center Team Lead/GE Manager Agent</t>
   </si>
   <si>
     <t>Dhaval Gosai</t>
   </si>
   <si>
-    <t>Ain Dubai</t>
-  </si>
-  <si>
-    <t>AD - Marketing</t>
-  </si>
-  <si>
-    <t>Influencer Visit</t>
+    <t>Dubai Parks™ and Resorts</t>
+  </si>
+  <si>
+    <t>Oasis Bay</t>
+  </si>
+  <si>
+    <t>Test Call Center Team Lead Manager</t>
+  </si>
+  <si>
+    <t>DPR-D2206-NR-SubmitForApproval</t>
+  </si>
+  <si>
+    <t>Attractions</t>
+  </si>
+  <si>
+    <t>Cricket</t>
+  </si>
+  <si>
+    <t>DPR-D2206-NR-OnHold</t>
+  </si>
+  <si>
+    <t>Bowling</t>
+  </si>
+  <si>
+    <t>DPR-D2206-Ref-Escalated</t>
+  </si>
+  <si>
+    <t>F&amp;B</t>
+  </si>
+  <si>
+    <t>The Keg</t>
+  </si>
+  <si>
+    <t>DPR - Refund</t>
+  </si>
+  <si>
+    <t>Attraction Closure</t>
   </si>
   <si>
     <t>Vincent Aslarona</t>
   </si>
   <si>
-    <t>AinDubai-D2204-NR-AssignedToAsset</t>
-  </si>
-  <si>
-    <t>Test Call Center Team Lead Manager</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-NR-AssignedToAsset</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-NR-OnHold</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-NR-InProgress</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-NR-Closed</t>
-  </si>
-  <si>
-    <t>Test Guest Experience Team Lead/Supervisor</t>
-  </si>
-  <si>
-    <t>Ivaylo Saraliev</t>
-  </si>
-  <si>
-    <t>AD - Incident</t>
-  </si>
-  <si>
-    <t>Medical (Low)</t>
-  </si>
-  <si>
-    <t>AD - Complaints</t>
-  </si>
-  <si>
-    <t>Serious, Escalated or VIP</t>
-  </si>
-  <si>
-    <t>Collaboration</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-Ref-Reopened</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-Ref-Escalated</t>
-  </si>
-  <si>
-    <t>AinDubai-D2206-Ref-Cancelled</t>
-  </si>
-  <si>
-    <t>AD - Ticketing</t>
+    <t>DPR-D2206-Ref-Cancelled</t>
+  </si>
+  <si>
+    <t>Chickadees</t>
   </si>
   <si>
     <t>Change of date</t>
   </si>
   <si>
-    <t>Double payment</t>
-  </si>
-  <si>
-    <t>Attraction closure</t>
+    <t>DPR-D2206-Ref-Reopened</t>
+  </si>
+  <si>
+    <t>OB - Refund</t>
+  </si>
+  <si>
+    <t>Change of Mind</t>
+  </si>
+  <si>
+    <t>Riverland™ Dubai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -178,10 +170,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,19 +511,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.9140625" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,187 +543,167 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C6" si="0">B2</f>
+        <v>DPR-D2206-NR-SubmitForApproval</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>DPR-D2206-NR-OnHold</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>DPR-D2206-Ref-Escalated</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>DPR-D2206-Ref-Cancelled</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>DPR-D2206-Ref-Reopened</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="str">
-        <f>B3</f>
-        <v>AinDubai-D2206-NR-OnHold</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="str">
-        <f t="shared" ref="C4:C8" si="0">B4</f>
-        <v>AinDubai-D2206-NR-InProgress</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>AinDubai-D2206-NR-Closed</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>AinDubai-D2206-Ref-Reopened</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>AinDubai-D2206-Ref-Escalated</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="1" t="s">
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>AinDubai-D2206-Ref-Cancelled</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 D2:H2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K1 A2:E2 G2:K2 A6:K11 A3:E3 G3:K3 A4:E4 G4:K4 A5:E5 G5:K5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/create-cases.xlsx
+++ b/data/create-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgosai\dhavalautomation-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFD6E08-844B-409D-B706-54E04F6966F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AA99CC-895C-4358-B56F-C92011C38973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15510" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
   <si>
     <t>User</t>
   </si>
@@ -53,12 +53,6 @@
     <t>Sub Asset</t>
   </si>
   <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Sub-Area</t>
-  </si>
-  <si>
     <t>Case Type</t>
   </si>
   <si>
@@ -68,73 +62,79 @@
     <t>Case Number</t>
   </si>
   <si>
-    <t>Test Call Center Team Lead/GE Manager Agent</t>
+    <t>Vincent Aslarona</t>
   </si>
   <si>
     <t>Dhaval Gosai</t>
   </si>
   <si>
-    <t>Dubai Parks™ and Resorts</t>
-  </si>
-  <si>
-    <t>Oasis Bay</t>
+    <t>Ain Dubai</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AD - Marketing</t>
+  </si>
+  <si>
+    <t>Influencer Visit</t>
   </si>
   <si>
     <t>Test Call Center Team Lead Manager</t>
   </si>
   <si>
-    <t>DPR-D2206-NR-SubmitForApproval</t>
-  </si>
-  <si>
-    <t>Attractions</t>
-  </si>
-  <si>
-    <t>Cricket</t>
-  </si>
-  <si>
-    <t>DPR-D2206-NR-OnHold</t>
-  </si>
-  <si>
-    <t>Bowling</t>
-  </si>
-  <si>
-    <t>DPR-D2206-Ref-Escalated</t>
-  </si>
-  <si>
-    <t>F&amp;B</t>
-  </si>
-  <si>
-    <t>The Keg</t>
-  </si>
-  <si>
-    <t>DPR - Refund</t>
-  </si>
-  <si>
-    <t>Attraction Closure</t>
-  </si>
-  <si>
-    <t>Vincent Aslarona</t>
-  </si>
-  <si>
-    <t>DPR-D2206-Ref-Cancelled</t>
-  </si>
-  <si>
-    <t>Chickadees</t>
+    <t>AD - Incident</t>
+  </si>
+  <si>
+    <t>Medical (Low)</t>
+  </si>
+  <si>
+    <t>AD - Complaints</t>
+  </si>
+  <si>
+    <t>Serious, Escalated or VIP</t>
+  </si>
+  <si>
+    <t>Test Guest Experience Team Lead/Supervisor</t>
+  </si>
+  <si>
+    <t>Collaboration</t>
+  </si>
+  <si>
+    <t>AD - Ticketing</t>
+  </si>
+  <si>
+    <t>Attraction closure</t>
+  </si>
+  <si>
+    <t>Double payment</t>
+  </si>
+  <si>
+    <t>Ivaylo Saraliev</t>
   </si>
   <si>
     <t>Change of date</t>
   </si>
   <si>
-    <t>DPR-D2206-Ref-Reopened</t>
-  </si>
-  <si>
-    <t>OB - Refund</t>
-  </si>
-  <si>
-    <t>Change of Mind</t>
-  </si>
-  <si>
-    <t>Riverland™ Dubai</t>
+    <t>AinDubai-D2506-NR-AssignedToAsset</t>
+  </si>
+  <si>
+    <t>AinDubai-D2506-NR-OnHold</t>
+  </si>
+  <si>
+    <t>AinDubai-D2506-NR-InProgress</t>
+  </si>
+  <si>
+    <t>AinDubai-D2506-NR-Closed</t>
+  </si>
+  <si>
+    <t>AinDubai-D2506-Ref-Reopened</t>
+  </si>
+  <si>
+    <t>AinDubai-D2506-Ref-Escalated</t>
+  </si>
+  <si>
+    <t>AinDubai-D2506-Ref-Cancelled</t>
   </si>
 </sst>
 </file>
@@ -511,14 +511,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="32.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,164 +545,181 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C8" si="0">B3</f>
+        <v>AinDubai-D2506-NR-OnHold</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="str">
-        <f t="shared" ref="C2:C6" si="0">B2</f>
-        <v>DPR-D2206-NR-SubmitForApproval</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" si="0"/>
-        <v>DPR-D2206-NR-OnHold</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
-        <v>DPR-D2206-Ref-Escalated</v>
+        <v>AinDubai-D2506-NR-InProgress</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
-        <v>DPR-D2206-Ref-Cancelled</v>
+        <v>AinDubai-D2506-NR-Closed</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
-        <v>DPR-D2206-Ref-Reopened</v>
+        <v>AinDubai-D2506-Ref-Reopened</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>32</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>AinDubai-D2506-Ref-Escalated</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>AinDubai-D2506-Ref-Cancelled</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A2:E2 G2:K2 A6:K11 A3:E3 G3:K3 A4:E4 G4:K4 A5:E5 G5:K5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A8 A2 D2:H2 A3 C3:H3 A4 C4:H4 A5 C5:H5 A6 C6:H6 A7 C7:H7 C8:H8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>